--- a/Thread Chart/Edwards Thread Charts.xlsx
+++ b/Thread Chart/Edwards Thread Charts.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\fs1\InformationManagement\Procedures &amp; References\Embroidery Thread Charts\Completed\Edwards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34DD2C87-F1A9-4624-9951-74EE03F00C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BDDCE3EE-84F3-4DC4-82A7-1484DE6FDDD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22920" yWindow="-1095" windowWidth="29040" windowHeight="15840" xr2:uid="{F028543A-CA1A-4C22-838B-894A262A5CAB}"/>
+    <workbookView xWindow="19090" yWindow="-5720" windowWidth="38620" windowHeight="21100" xr2:uid="{F028543A-CA1A-4C22-838B-894A262A5CAB}"/>
   </bookViews>
   <sheets>
     <sheet name="RA Super Brite Poly" sheetId="3" r:id="rId1"/>
+    <sheet name="Madeira Polyneon" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RA Super Brite Poly'!$A$1:$I$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Madeira Polyneon'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RA Super Brite Poly'!$A$1:$I$154</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +28,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="184">
   <si>
     <t>Thread Name</t>
   </si>
@@ -48,6 +55,9 @@
     <t>Thread Number</t>
   </si>
   <si>
+    <t>Monitor Display Color</t>
+  </si>
+  <si>
     <t>PMS Number</t>
   </si>
   <si>
@@ -60,509 +70,536 @@
     <t>B</t>
   </si>
   <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>Blacks</t>
+  </si>
+  <si>
+    <t>SBP-9</t>
+  </si>
+  <si>
+    <t>BlackC</t>
+  </si>
+  <si>
+    <t>Sky Blue</t>
+  </si>
+  <si>
+    <t>Blues</t>
+  </si>
+  <si>
+    <t>Herbal Blue</t>
+  </si>
+  <si>
+    <t>Bambino Blue</t>
+  </si>
+  <si>
+    <t>Lake Blue</t>
+  </si>
+  <si>
+    <t>Blue Splendor</t>
+  </si>
+  <si>
+    <t>Amanda Lavender</t>
+  </si>
+  <si>
+    <t>Blue Wisteria</t>
+  </si>
+  <si>
+    <t>Jay Blue</t>
+  </si>
+  <si>
+    <t>California Blue</t>
+  </si>
+  <si>
+    <t>Copen</t>
+  </si>
+  <si>
+    <t>Oriental Blue</t>
+  </si>
+  <si>
+    <t>Blue</t>
+  </si>
+  <si>
+    <t>Sapphire</t>
+  </si>
+  <si>
+    <t>Slate Blue</t>
+  </si>
+  <si>
+    <t>Blue Moon</t>
+  </si>
+  <si>
+    <t>Baltic Blue</t>
+  </si>
+  <si>
+    <t>Imperial Blue</t>
+  </si>
+  <si>
+    <t>Blue Suede</t>
+  </si>
+  <si>
+    <t>Royal</t>
+  </si>
+  <si>
+    <t>Peacock</t>
+  </si>
+  <si>
+    <t>Favorite Deep Blue</t>
+  </si>
+  <si>
+    <t>Light Midnight</t>
+  </si>
+  <si>
+    <t>Venus Blue</t>
+  </si>
+  <si>
+    <t>Light Navy</t>
+  </si>
+  <si>
+    <t>Perpetual Teal</t>
+  </si>
+  <si>
+    <t>Blue Ribbon</t>
+  </si>
+  <si>
+    <t>PN Navy</t>
+  </si>
+  <si>
+    <t>Smokey</t>
+  </si>
+  <si>
+    <t>7547C</t>
+  </si>
+  <si>
+    <t>Ivory</t>
+  </si>
+  <si>
+    <t>Browns</t>
+  </si>
+  <si>
+    <t>Seashell</t>
+  </si>
+  <si>
+    <t>Tan</t>
+  </si>
+  <si>
+    <t>Ashley Gold</t>
+  </si>
+  <si>
+    <t>Basket Beige</t>
+  </si>
+  <si>
+    <t>Golden Tan</t>
+  </si>
+  <si>
+    <t>Beige</t>
+  </si>
+  <si>
+    <t>Almond</t>
+  </si>
+  <si>
+    <t>Copper</t>
+  </si>
+  <si>
+    <t>Taupe</t>
+  </si>
+  <si>
+    <t>Bronze</t>
+  </si>
+  <si>
+    <t>Hazel</t>
+  </si>
+  <si>
+    <t>Happy Trail</t>
+  </si>
+  <si>
+    <t>Cocoa Mulch</t>
+  </si>
+  <si>
+    <t>Sand Dune</t>
+  </si>
+  <si>
+    <t>Chocolate</t>
+  </si>
+  <si>
+    <t>Lt. Cocoa</t>
+  </si>
+  <si>
+    <t>Brownstone</t>
+  </si>
+  <si>
+    <t>Dark Brown</t>
+  </si>
+  <si>
+    <t>Mahogany</t>
+  </si>
+  <si>
+    <t>Steel Gray</t>
+  </si>
+  <si>
+    <t>Grays</t>
+  </si>
+  <si>
+    <t>Teardrop Grey</t>
+  </si>
+  <si>
+    <t>Skylight</t>
+  </si>
+  <si>
+    <t>Titanium</t>
+  </si>
+  <si>
+    <t>Cool Gray 3</t>
+  </si>
+  <si>
+    <t>Turkish Tan</t>
+  </si>
+  <si>
+    <t>Otter Gray</t>
+  </si>
+  <si>
+    <t>Carbondale</t>
+  </si>
+  <si>
+    <t>Silvery Gray</t>
+  </si>
+  <si>
+    <t>Gray Flannel</t>
+  </si>
+  <si>
+    <t>Charcoal</t>
+  </si>
+  <si>
+    <t>Warm Gray 11</t>
+  </si>
+  <si>
+    <t>Metal</t>
+  </si>
+  <si>
+    <t>Aged Charcoal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black 7 </t>
+  </si>
+  <si>
+    <t>Celery</t>
+  </si>
+  <si>
+    <t>Greens</t>
+  </si>
+  <si>
+    <t>Glendale</t>
+  </si>
+  <si>
+    <t>Sprite</t>
+  </si>
+  <si>
+    <t>Green Oak</t>
+  </si>
+  <si>
+    <t>Tealeaf</t>
+  </si>
+  <si>
+    <t>Rolling Meadow</t>
+  </si>
+  <si>
+    <t>Limerick</t>
+  </si>
+  <si>
+    <t>Seafoam</t>
+  </si>
+  <si>
+    <t>Kiwi Green</t>
+  </si>
+  <si>
+    <t>Erin Green</t>
+  </si>
+  <si>
+    <t>Foliage Green</t>
+  </si>
+  <si>
+    <t>Peapod</t>
+  </si>
+  <si>
+    <t>Ming</t>
+  </si>
+  <si>
+    <t>J Turquoise</t>
+  </si>
+  <si>
+    <t>Isle Green</t>
+  </si>
+  <si>
+    <t>Veggie Green</t>
+  </si>
+  <si>
+    <t>Bonaire Green</t>
+  </si>
+  <si>
+    <t>Teal</t>
+  </si>
+  <si>
+    <t>Olive</t>
+  </si>
+  <si>
+    <t>Spruce</t>
+  </si>
+  <si>
+    <t>Light Kelly</t>
+  </si>
+  <si>
+    <t>Dark Green</t>
+  </si>
+  <si>
+    <t>Pine Green</t>
+  </si>
+  <si>
+    <t>Willow</t>
+  </si>
+  <si>
+    <t>Kelly</t>
+  </si>
+  <si>
+    <t>Green Forest</t>
+  </si>
+  <si>
+    <t>Mars Green</t>
+  </si>
+  <si>
+    <t>Green Bay</t>
+  </si>
+  <si>
+    <t>Alpine Green</t>
+  </si>
+  <si>
+    <t>Olive Drab</t>
+  </si>
+  <si>
+    <t>Evergreen</t>
+  </si>
+  <si>
+    <t>Blue Spruce</t>
+  </si>
+  <si>
+    <t>Gov't Gold</t>
+  </si>
+  <si>
+    <t>Metallics</t>
+  </si>
+  <si>
+    <t>Silver</t>
+  </si>
+  <si>
+    <t>CG1</t>
+  </si>
+  <si>
+    <t>Sunburst</t>
+  </si>
+  <si>
+    <t>Oranges</t>
+  </si>
+  <si>
+    <t>Golden Poppy</t>
+  </si>
+  <si>
+    <t>Singh Mist</t>
+  </si>
+  <si>
+    <t>Orange</t>
+  </si>
+  <si>
+    <t>Dark Texas Orange</t>
+  </si>
+  <si>
+    <t>Paprika</t>
+  </si>
+  <si>
+    <t>Grilled Orange</t>
+  </si>
+  <si>
+    <t>Rust</t>
+  </si>
+  <si>
+    <t>Honeysuckle</t>
+  </si>
+  <si>
+    <t>Light Pink</t>
+  </si>
+  <si>
+    <t>Pinks</t>
+  </si>
+  <si>
+    <t>Pink</t>
+  </si>
+  <si>
+    <t>Carnation</t>
+  </si>
+  <si>
+    <t>Salmon</t>
+  </si>
+  <si>
+    <t>Horizon Pink</t>
+  </si>
+  <si>
+    <t>Bitteroot</t>
+  </si>
+  <si>
+    <t>Passion</t>
+  </si>
+  <si>
+    <t>Cherry Stone</t>
+  </si>
+  <si>
+    <t>Tulip</t>
+  </si>
+  <si>
+    <t>Purples</t>
+  </si>
+  <si>
+    <t>Pansy Purple</t>
+  </si>
+  <si>
+    <t>Plum</t>
+  </si>
+  <si>
+    <t>Lucky Lavender</t>
+  </si>
+  <si>
+    <t>Cindy Purple</t>
+  </si>
+  <si>
+    <t>Purple Chariot</t>
+  </si>
+  <si>
+    <t>Dark Melody</t>
+  </si>
+  <si>
+    <t>Purple</t>
+  </si>
+  <si>
+    <t>Regal Purple</t>
+  </si>
+  <si>
+    <t>Purple Ice</t>
+  </si>
+  <si>
+    <t>Salvia Plum</t>
+  </si>
+  <si>
+    <t>May Nights</t>
+  </si>
+  <si>
+    <t>Indian Summer</t>
+  </si>
+  <si>
+    <t>Reds</t>
+  </si>
+  <si>
+    <t>Radiant Red</t>
+  </si>
+  <si>
+    <t>Foxy Red</t>
+  </si>
+  <si>
+    <t>Red</t>
+  </si>
+  <si>
+    <t>Toasty Red</t>
+  </si>
+  <si>
+    <t>Candy Apple Red</t>
+  </si>
+  <si>
+    <t>Burgundy</t>
+  </si>
+  <si>
+    <t>Russet</t>
+  </si>
+  <si>
+    <t>Terra Cotta</t>
+  </si>
+  <si>
+    <t>Warm Wine</t>
+  </si>
+  <si>
+    <t>Snow White</t>
+  </si>
+  <si>
+    <t>Whites</t>
+  </si>
+  <si>
+    <t>Trans. White</t>
+  </si>
+  <si>
+    <t>Eggshell</t>
+  </si>
+  <si>
+    <t>Yellows</t>
+  </si>
+  <si>
+    <t>Ice Ballet</t>
+  </si>
+  <si>
+    <t>Foundation</t>
+  </si>
+  <si>
+    <t>Visor Gold</t>
+  </si>
+  <si>
+    <t>Lemon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neon Yellow </t>
+  </si>
+  <si>
+    <t>Sunflower</t>
+  </si>
+  <si>
+    <t>Goldenrod</t>
+  </si>
+  <si>
+    <t>Warm Sunshine</t>
+  </si>
+  <si>
+    <t>Scholastic</t>
+  </si>
+  <si>
+    <t>Pooh</t>
+  </si>
+  <si>
+    <t>Ombre Gold</t>
+  </si>
+  <si>
     <t>Yellow</t>
   </si>
   <si>
-    <t>Goldenrod</t>
-  </si>
-  <si>
-    <t>Lemon</t>
-  </si>
-  <si>
-    <t>Eggshell</t>
-  </si>
-  <si>
-    <t>Visor Gold</t>
-  </si>
-  <si>
     <t>Yellow Mist</t>
   </si>
   <si>
-    <t>Sunflower</t>
-  </si>
-  <si>
-    <t>Scholastic</t>
+    <t>Rice Paper</t>
+  </si>
+  <si>
+    <t>Cloth of Gold</t>
+  </si>
+  <si>
+    <t>TH Gold</t>
   </si>
   <si>
     <t>Shimmering Gold</t>
   </si>
   <si>
-    <t>TH Gold</t>
-  </si>
-  <si>
-    <t>Grays</t>
-  </si>
-  <si>
-    <t>Charcoal</t>
-  </si>
-  <si>
-    <t>Warm Gray 11</t>
-  </si>
-  <si>
-    <t>Steel Gray</t>
-  </si>
-  <si>
-    <t>Metal</t>
-  </si>
-  <si>
-    <t>Skylight</t>
-  </si>
-  <si>
-    <t>Silvery Gray</t>
-  </si>
-  <si>
-    <t>Aged Charcoal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black 7 </t>
-  </si>
-  <si>
-    <t>Rust</t>
-  </si>
-  <si>
-    <t>Golden Poppy</t>
-  </si>
-  <si>
-    <t>Honeysuckle</t>
-  </si>
-  <si>
-    <t>Blue</t>
-  </si>
-  <si>
-    <t>Royal</t>
-  </si>
-  <si>
-    <t>Sky Blue</t>
-  </si>
-  <si>
-    <t>Copen</t>
-  </si>
-  <si>
-    <t>Sapphire</t>
-  </si>
-  <si>
-    <t>Oriental Blue</t>
-  </si>
-  <si>
-    <t>Imperial Blue</t>
-  </si>
-  <si>
-    <t>Light Navy</t>
-  </si>
-  <si>
-    <t>Jay Blue</t>
-  </si>
-  <si>
-    <t>Light Midnight</t>
-  </si>
-  <si>
-    <t>California Blue</t>
-  </si>
-  <si>
-    <t>Blue Suede</t>
-  </si>
-  <si>
-    <t>Blue Ribbon</t>
-  </si>
-  <si>
-    <t>Red</t>
-  </si>
-  <si>
-    <t>Burgundy</t>
-  </si>
-  <si>
-    <t>Russet</t>
-  </si>
-  <si>
-    <t>Foxy Red</t>
-  </si>
-  <si>
-    <t>Radiant Red</t>
-  </si>
-  <si>
-    <t>Terra Cotta</t>
-  </si>
-  <si>
-    <t>Warm Wine</t>
-  </si>
-  <si>
-    <t>Candy Apple Red</t>
-  </si>
-  <si>
-    <t>Purple</t>
-  </si>
-  <si>
-    <t>Tulip</t>
-  </si>
-  <si>
-    <t>Plum</t>
-  </si>
-  <si>
-    <t>Olive</t>
-  </si>
-  <si>
-    <t>Greens</t>
-  </si>
-  <si>
-    <t>Purples</t>
-  </si>
-  <si>
-    <t>Reds</t>
-  </si>
-  <si>
-    <t>Blues</t>
-  </si>
-  <si>
-    <t>Oranges</t>
-  </si>
-  <si>
-    <t>Yellows</t>
-  </si>
-  <si>
-    <t>Dark Green</t>
-  </si>
-  <si>
-    <t>Willow</t>
-  </si>
-  <si>
-    <t>Spruce</t>
-  </si>
-  <si>
-    <t>Teal</t>
-  </si>
-  <si>
-    <t>Isle Green</t>
-  </si>
-  <si>
-    <t>Evergreen</t>
-  </si>
-  <si>
-    <t>Celery</t>
-  </si>
-  <si>
-    <t>Olive Drab</t>
-  </si>
-  <si>
-    <t>Green Oak</t>
-  </si>
-  <si>
-    <t>Erin Green</t>
-  </si>
-  <si>
-    <t>Ming</t>
-  </si>
-  <si>
-    <t>Pine Green</t>
-  </si>
-  <si>
-    <t>Green Bay</t>
-  </si>
-  <si>
-    <t>Peapod</t>
-  </si>
-  <si>
-    <t>J Turquoise</t>
-  </si>
-  <si>
-    <t>Foliage Green</t>
-  </si>
-  <si>
-    <t>Blue Spruce</t>
-  </si>
-  <si>
-    <t>Browns</t>
-  </si>
-  <si>
-    <t>Beige</t>
-  </si>
-  <si>
-    <t>Chocolate</t>
-  </si>
-  <si>
-    <t>Tan</t>
-  </si>
-  <si>
-    <t>Copper</t>
-  </si>
-  <si>
-    <t>Taupe</t>
-  </si>
-  <si>
-    <t>Ivory</t>
-  </si>
-  <si>
-    <t>Dark Brown</t>
-  </si>
-  <si>
-    <t>Ashley Gold</t>
-  </si>
-  <si>
-    <t>Seashell</t>
-  </si>
-  <si>
-    <t>Lt. Cocoa</t>
-  </si>
-  <si>
-    <t>Sand Dune</t>
-  </si>
-  <si>
-    <t>Almond</t>
-  </si>
-  <si>
-    <t>Hazel</t>
-  </si>
-  <si>
-    <t>Mahogany</t>
-  </si>
-  <si>
-    <t>Golden Tan</t>
-  </si>
-  <si>
-    <t>Pink</t>
-  </si>
-  <si>
-    <t>Pinks</t>
-  </si>
-  <si>
-    <t>Carnation</t>
-  </si>
-  <si>
-    <t>Light Pink</t>
-  </si>
-  <si>
-    <t>Salmon</t>
-  </si>
-  <si>
-    <t>Cherry Stone</t>
-  </si>
-  <si>
-    <t>Monitor Display Color</t>
-  </si>
-  <si>
-    <t>Black</t>
-  </si>
-  <si>
-    <t>Blacks</t>
-  </si>
-  <si>
-    <t>BlackC</t>
-  </si>
-  <si>
-    <t>Snow White</t>
-  </si>
-  <si>
-    <t>Whites</t>
-  </si>
-  <si>
-    <t>Trans. White</t>
-  </si>
-  <si>
-    <t>Basket Beige</t>
-  </si>
-  <si>
-    <t>Ice Ballet</t>
-  </si>
-  <si>
-    <t>Ombre Gold</t>
-  </si>
-  <si>
-    <t>Pooh</t>
-  </si>
-  <si>
-    <t>Sunburst</t>
-  </si>
-  <si>
-    <t>Bitteroot</t>
-  </si>
-  <si>
-    <t>Indian Summer</t>
-  </si>
-  <si>
-    <t>Grilled Orange</t>
-  </si>
-  <si>
-    <t>Dark Texas Orange</t>
-  </si>
-  <si>
-    <t>Singh Mist</t>
-  </si>
-  <si>
-    <t>Foundation</t>
-  </si>
-  <si>
-    <t>Rice Paper</t>
-  </si>
-  <si>
-    <t>Bronze</t>
-  </si>
-  <si>
-    <t>Happy Trail</t>
-  </si>
-  <si>
-    <t>Cocoa Mulch</t>
-  </si>
-  <si>
-    <t>Brownstone</t>
-  </si>
-  <si>
-    <t>Cloth of Gold</t>
-  </si>
-  <si>
-    <t>Horizon Pink</t>
-  </si>
-  <si>
-    <t>Passion</t>
-  </si>
-  <si>
-    <t>Toasty Red</t>
-  </si>
-  <si>
-    <t>Salvia Plum</t>
-  </si>
-  <si>
-    <t>Pansy Purple</t>
-  </si>
-  <si>
-    <t>Purple Ice</t>
-  </si>
-  <si>
-    <t>Cindy Purple</t>
-  </si>
-  <si>
-    <t>May Nights</t>
-  </si>
-  <si>
-    <t>Lucky Lavender</t>
-  </si>
-  <si>
-    <t>Purple Chariot</t>
-  </si>
-  <si>
-    <t>Dark Melody</t>
-  </si>
-  <si>
-    <t>Regal Purple</t>
-  </si>
-  <si>
-    <t>Amanda Lavender</t>
-  </si>
-  <si>
-    <t>Bambino Blue</t>
-  </si>
-  <si>
-    <t>Blue Splendor</t>
-  </si>
-  <si>
-    <t>Blue Moon</t>
-  </si>
-  <si>
-    <t>Baltic Blue</t>
-  </si>
-  <si>
-    <t>Favorite Deep Blue</t>
-  </si>
-  <si>
-    <t>PN Navy</t>
-  </si>
-  <si>
-    <t>Peacock</t>
-  </si>
-  <si>
-    <t>Venus Blue</t>
-  </si>
-  <si>
-    <t>Perpetual Teal</t>
-  </si>
-  <si>
-    <t>Blue Wisteria</t>
-  </si>
-  <si>
-    <t>Mystic Teal</t>
-  </si>
-  <si>
-    <t>Herbal Blue</t>
-  </si>
-  <si>
-    <t>Sprite</t>
-  </si>
-  <si>
-    <t>Tealeaf</t>
-  </si>
-  <si>
-    <t>Seafoam</t>
-  </si>
-  <si>
-    <t>Green Forest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neon Yellow </t>
-  </si>
-  <si>
-    <t>Glendale</t>
-  </si>
-  <si>
-    <t>Rolling Meadow</t>
-  </si>
-  <si>
-    <t>Limerick</t>
-  </si>
-  <si>
-    <t>Mars Green</t>
-  </si>
-  <si>
-    <t>Alpine Green</t>
-  </si>
-  <si>
-    <t>Titanium</t>
-  </si>
-  <si>
-    <t>Teardrop Grey</t>
-  </si>
-  <si>
-    <t>Otter Gray</t>
-  </si>
-  <si>
-    <t>Turkish Tan</t>
-  </si>
-  <si>
-    <t>Carbondale</t>
-  </si>
-  <si>
-    <t>Gray Flannel</t>
-  </si>
-  <si>
-    <t>Cool Gray 3</t>
-  </si>
-  <si>
-    <t>Veggie Green</t>
-  </si>
-  <si>
-    <t>Kiwi Green</t>
-  </si>
-  <si>
-    <t>Bonaire Green</t>
-  </si>
-  <si>
-    <t>SBP-9</t>
-  </si>
-  <si>
-    <t>Lake Blue</t>
-  </si>
-  <si>
-    <t>Fleet Blue</t>
-  </si>
-  <si>
-    <t>Pistachio</t>
-  </si>
-  <si>
-    <t>Havana Yellow</t>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Madeira Polyneon</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -585,8 +622,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="144">
+  <fills count="148">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1231,12 +1281,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00A5B4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF9CDAD9"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1423,25 +1467,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF081D40"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3A96C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE9F600"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC700"/>
+        <fgColor rgb="FF007831"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF660A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4E6793"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF151D27"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF378F3D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3B87B"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB08414"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAD9D7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1458,7 +1532,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1781,10 +1855,10 @@
     <xf numFmtId="0" fontId="0" fillId="107" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="108" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="109" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="108" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="109" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="110" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1883,10 +1957,25 @@
     <xf numFmtId="0" fontId="0" fillId="141" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="142" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="142" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="143" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="144" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="145" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="146" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="147" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2217,8 +2306,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F5A48E9-F316-4B13-8BCA-A06BACA98426}">
-  <dimension ref="A1:I158"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O163"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" style="1" customWidth="1"/>
@@ -2226,14 +2315,14 @@
     <col min="4" max="4" width="19.7109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="17.7109375" style="1" customWidth="1"/>
-    <col min="7" max="9" width="8.85546875" style="1"/>
-    <col min="10" max="10" width="20.7109375" style="1" customWidth="1"/>
-    <col min="11" max="14" width="8.85546875" style="1"/>
-    <col min="15" max="15" width="50.7109375" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.85546875" style="1"/>
+    <col min="7" max="9" width="8.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" style="1" hidden="1" customWidth="1"/>
+    <col min="11" max="14" width="8.85546875" style="1" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="50.7109375" style="1" hidden="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.85546875" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="3" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="3" customFormat="1" ht="50.1" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2247,37 +2336,37 @@
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="50.1" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>101</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>102</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D2" s="1">
         <v>5596</v>
       </c>
       <c r="E2" s="98"/>
       <c r="F2" s="1" t="s">
-        <v>103</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
@@ -2289,15 +2378,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="50.1" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1">
         <v>5539</v>
@@ -2316,20 +2405,20 @@
         <v>233</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="50.1" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>148</v>
+        <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D4" s="1">
         <v>9103</v>
       </c>
-      <c r="E4" s="109"/>
+      <c r="E4" s="108"/>
       <c r="F4" s="1">
         <v>324</v>
       </c>
@@ -2343,15 +2432,15 @@
         <v>217</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="50.1" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>137</v>
+        <v>16</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D5" s="1">
         <v>9079</v>
@@ -2370,15 +2459,15 @@
         <v>228</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="50.1" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>170</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D6" s="1">
         <v>5604</v>
@@ -2397,15 +2486,15 @@
         <v>226</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="50.1" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>138</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D7" s="1">
         <v>9039</v>
@@ -2424,15 +2513,15 @@
         <v>226</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="50.1" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D8" s="1">
         <v>9048</v>
@@ -2451,180 +2540,180 @@
         <v>219</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="50.1" customHeight="1">
       <c r="A9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="1">
+        <v>9052</v>
+      </c>
+      <c r="E9" s="107"/>
+      <c r="F9" s="1">
+        <v>7703</v>
+      </c>
+      <c r="G9" s="1">
+        <v>8</v>
+      </c>
+      <c r="H9" s="1">
+        <v>154</v>
+      </c>
+      <c r="I9" s="1">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="1">
+        <v>5684</v>
+      </c>
+      <c r="E10" s="36"/>
+      <c r="F10" s="1">
+        <v>2718</v>
+      </c>
+      <c r="G10" s="1">
+        <v>90</v>
+      </c>
+      <c r="H10" s="1">
+        <v>135</v>
+      </c>
+      <c r="I10" s="1">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1">
+        <v>5689</v>
+      </c>
+      <c r="E11" s="38"/>
+      <c r="F11" s="1">
+        <v>639</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
         <v>147</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D9" s="1">
-        <v>5743</v>
-      </c>
-      <c r="E9" s="108"/>
-      <c r="F9" s="1">
-        <v>7710</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0</v>
-      </c>
-      <c r="H9" s="1">
-        <v>165</v>
-      </c>
-      <c r="I9" s="1">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D10" s="1">
-        <v>9052</v>
-      </c>
-      <c r="E10" s="107"/>
-      <c r="F10" s="1">
-        <v>7703</v>
-      </c>
-      <c r="G10" s="1">
-        <v>8</v>
-      </c>
-      <c r="H10" s="1">
-        <v>154</v>
-      </c>
-      <c r="I10" s="1">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D11" s="1">
-        <v>5684</v>
-      </c>
-      <c r="E11" s="36"/>
-      <c r="F11" s="1">
-        <v>2718</v>
-      </c>
-      <c r="G11" s="1">
-        <v>90</v>
-      </c>
-      <c r="H11" s="1">
-        <v>135</v>
-      </c>
       <c r="I11" s="1">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="50.1" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D12" s="1">
-        <v>5689</v>
-      </c>
-      <c r="E12" s="38"/>
+        <v>5545</v>
+      </c>
+      <c r="E12" s="31"/>
       <c r="F12" s="1">
-        <v>639</v>
+        <v>279</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="H12" s="1">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="I12" s="1">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="50.1" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D13" s="1">
-        <v>5545</v>
-      </c>
-      <c r="E13" s="31"/>
+        <v>5601</v>
+      </c>
+      <c r="E13" s="32"/>
       <c r="F13" s="1">
-        <v>279</v>
+        <v>2143</v>
       </c>
       <c r="G13" s="1">
         <v>62</v>
       </c>
       <c r="H13" s="1">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="I13" s="1">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="50.1" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D14" s="1">
-        <v>5601</v>
-      </c>
-      <c r="E14" s="32"/>
+        <v>5520</v>
+      </c>
+      <c r="E14" s="29"/>
       <c r="F14" s="1">
-        <v>2143</v>
+        <v>2728</v>
       </c>
       <c r="G14" s="1">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="H14" s="1">
-        <v>133</v>
+        <v>70</v>
       </c>
       <c r="I14" s="1">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="50.1" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D15" s="1">
-        <v>5520</v>
+        <v>5580</v>
       </c>
       <c r="E15" s="29"/>
       <c r="F15" s="1">
@@ -2640,42 +2729,42 @@
         <v>185</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="50.1" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D16" s="1">
-        <v>5580</v>
-      </c>
-      <c r="E16" s="29"/>
+        <v>5575</v>
+      </c>
+      <c r="E16" s="142"/>
       <c r="F16" s="1">
-        <v>2728</v>
+        <v>2139</v>
       </c>
       <c r="G16" s="1">
+        <v>78</v>
+      </c>
+      <c r="H16" s="1">
+        <v>103</v>
+      </c>
+      <c r="I16" s="1">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H16" s="1">
-        <v>70</v>
-      </c>
-      <c r="I16" s="1">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="C17" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D17" s="1">
         <v>9081</v>
@@ -2694,15 +2783,15 @@
         <v>160</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="50.1" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>140</v>
+        <v>29</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D18" s="1">
         <v>5741</v>
@@ -2721,15 +2810,15 @@
         <v>150</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="50.1" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D19" s="1">
         <v>5602</v>
@@ -2748,15 +2837,15 @@
         <v>143</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="50.1" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D20" s="1">
         <v>5738</v>
@@ -2775,15 +2864,15 @@
         <v>159</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="50.1" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D21" s="1">
         <v>5510</v>
@@ -2802,15 +2891,15 @@
         <v>133</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="50.1" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>143</v>
+        <v>33</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D22" s="1">
         <v>5810</v>
@@ -2829,15 +2918,15 @@
         <v>126</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="50.1" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>141</v>
+        <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D23" s="1">
         <v>9075</v>
@@ -2856,15 +2945,15 @@
         <v>125</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="50.1" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D24" s="1">
         <v>5686</v>
@@ -2883,15 +2972,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="50.1" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>144</v>
+        <v>36</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D25" s="1">
         <v>9100</v>
@@ -2910,15 +2999,15 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="50.1" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D26" s="1">
         <v>5603</v>
@@ -2937,15 +3026,15 @@
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="50.1" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>145</v>
+        <v>38</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D27" s="1">
         <v>9062</v>
@@ -2964,15 +3053,15 @@
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="50.1" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D28" s="1">
         <v>5739</v>
@@ -2991,15 +3080,15 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="50.1" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>142</v>
+        <v>40</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D29" s="1">
         <v>5824</v>
@@ -3018,42 +3107,42 @@
         <v>74</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="50.1" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>171</v>
+        <v>41</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D30" s="1">
-        <v>5750</v>
-      </c>
-      <c r="E30" s="140"/>
-      <c r="F30" s="1">
-        <v>282</v>
+        <v>5787</v>
+      </c>
+      <c r="E30" s="143"/>
+      <c r="F30" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G30" s="1">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="H30" s="1">
         <v>29</v>
       </c>
       <c r="I30" s="1">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="50.1" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D31" s="1">
         <v>5635</v>
@@ -3072,15 +3161,15 @@
         <v>176</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="50.1" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D32" s="1">
         <v>5776</v>
@@ -3099,15 +3188,15 @@
         <v>133</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" ht="50.1" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D33" s="1">
         <v>5573</v>
@@ -3126,15 +3215,15 @@
         <v>115</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" ht="50.1" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D34" s="1">
         <v>5701</v>
@@ -3153,20 +3242,20 @@
         <v>106</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" ht="50.1" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>107</v>
+        <v>48</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D35" s="1">
         <v>9126</v>
       </c>
-      <c r="E35" s="110"/>
+      <c r="E35" s="109"/>
       <c r="F35" s="1">
         <v>7528</v>
       </c>
@@ -3180,15 +3269,15 @@
         <v>172</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" ht="50.1" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D36" s="1">
         <v>5870</v>
@@ -3207,15 +3296,15 @@
         <v>117</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" ht="50.1" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D37" s="1">
         <v>5524</v>
@@ -3234,15 +3323,15 @@
         <v>92</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" ht="50.1" customHeight="1">
       <c r="A38" s="1" t="s">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D38" s="1">
         <v>5779</v>
@@ -3261,15 +3350,15 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" ht="50.1" customHeight="1">
       <c r="A39" s="1" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D39" s="1">
         <v>5595</v>
@@ -3288,15 +3377,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" ht="50.1" customHeight="1">
       <c r="A40" s="1" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D40" s="1">
         <v>5598</v>
@@ -3315,15 +3404,15 @@
         <v>126</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" ht="50.1" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>119</v>
+        <v>54</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D41" s="1">
         <v>5815</v>
@@ -3342,15 +3431,15 @@
         <v>126</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" ht="50.1" customHeight="1">
       <c r="A42" s="1" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D42" s="1">
         <v>5781</v>
@@ -3369,15 +3458,15 @@
         <v>37</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" ht="50.1" customHeight="1">
       <c r="A43" s="1" t="s">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D43" s="1">
         <v>9087</v>
@@ -3396,15 +3485,15 @@
         <v>115</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" ht="50.1" customHeight="1">
       <c r="A44" s="1" t="s">
-        <v>121</v>
+        <v>57</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D44" s="1">
         <v>5788</v>
@@ -3423,15 +3512,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" ht="50.1" customHeight="1">
       <c r="A45" s="1" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D45" s="1">
         <v>5777</v>
@@ -3450,15 +3539,15 @@
         <v>61</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" ht="50.1" customHeight="1">
       <c r="A46" s="1" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D46" s="1">
         <v>5527</v>
@@ -3477,15 +3566,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" ht="50.1" customHeight="1">
       <c r="A47" s="1" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D47" s="1">
         <v>5778</v>
@@ -3504,20 +3593,20 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" ht="50.1" customHeight="1">
       <c r="A48" s="1" t="s">
-        <v>122</v>
+        <v>61</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D48" s="1">
         <v>9042</v>
       </c>
-      <c r="E48" s="111"/>
+      <c r="E48" s="110"/>
       <c r="F48" s="1">
         <v>7517</v>
       </c>
@@ -3531,15 +3620,15 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" ht="50.1" customHeight="1">
       <c r="A49" s="1" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D49" s="1">
         <v>5672</v>
@@ -3558,15 +3647,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" ht="50.1" customHeight="1">
       <c r="A50" s="1" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D50" s="1">
         <v>5864</v>
@@ -3585,15 +3674,15 @@
         <v>43</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" ht="50.1" customHeight="1">
       <c r="A51" s="1" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D51" s="1">
         <v>5574</v>
@@ -3612,20 +3701,20 @@
         <v>224</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" ht="50.1" customHeight="1">
       <c r="A52" s="1" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D52" s="1">
         <v>9116</v>
       </c>
-      <c r="E52" s="113"/>
+      <c r="E52" s="112"/>
       <c r="F52" s="1">
         <v>428</v>
       </c>
@@ -3639,15 +3728,15 @@
         <v>199</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" ht="50.1" customHeight="1">
       <c r="A53" s="1" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D53" s="1">
         <v>5782</v>
@@ -3666,22 +3755,22 @@
         <v>209</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" ht="50.1" customHeight="1">
       <c r="A54" s="1" t="s">
-        <v>159</v>
+        <v>68</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D54" s="1">
         <v>9083</v>
       </c>
-      <c r="E54" s="112"/>
+      <c r="E54" s="111"/>
       <c r="F54" s="1" t="s">
-        <v>165</v>
+        <v>69</v>
       </c>
       <c r="G54" s="1">
         <v>201</v>
@@ -3693,20 +3782,20 @@
         <v>201</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" ht="50.1" customHeight="1">
       <c r="A55" s="1" t="s">
-        <v>162</v>
+        <v>70</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D55" s="1">
         <v>9134</v>
       </c>
-      <c r="E55" s="115"/>
+      <c r="E55" s="114"/>
       <c r="F55" s="1">
         <v>7536</v>
       </c>
@@ -3720,20 +3809,20 @@
         <v>135</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" ht="50.1" customHeight="1">
       <c r="A56" s="1" t="s">
-        <v>161</v>
+        <v>71</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D56" s="1">
         <v>9115</v>
       </c>
-      <c r="E56" s="114"/>
+      <c r="E56" s="113"/>
       <c r="F56" s="1">
         <v>443</v>
       </c>
@@ -3747,15 +3836,15 @@
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" ht="50.1" customHeight="1">
       <c r="A57" s="1" t="s">
-        <v>163</v>
+        <v>72</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D57" s="1">
         <v>9128</v>
@@ -3774,15 +3863,15 @@
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" ht="50.1" customHeight="1">
       <c r="A58" s="1" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D58" s="1">
         <v>5784</v>
@@ -3801,20 +3890,20 @@
         <v>139</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" ht="50.1" customHeight="1">
       <c r="A59" s="1" t="s">
-        <v>164</v>
+        <v>74</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D59" s="1">
         <v>9117</v>
       </c>
-      <c r="E59" s="116"/>
+      <c r="E59" s="115"/>
       <c r="F59" s="1">
         <v>424</v>
       </c>
@@ -3828,22 +3917,22 @@
         <v>113</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" ht="50.1" customHeight="1">
       <c r="A60" s="1" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D60" s="1">
         <v>5565</v>
       </c>
       <c r="E60" s="15"/>
       <c r="F60" s="1" t="s">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="G60" s="1">
         <v>111</v>
@@ -3855,15 +3944,15 @@
         <v>88</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" ht="50.1" customHeight="1">
       <c r="A61" s="1" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D61" s="1">
         <v>5707</v>
@@ -3882,22 +3971,22 @@
         <v>87</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" ht="50.1" customHeight="1">
       <c r="A62" s="1" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D62" s="1">
         <v>5865</v>
       </c>
       <c r="E62" s="20"/>
       <c r="F62" s="1" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="G62" s="1">
         <v>60</v>
@@ -3909,15 +3998,15 @@
         <v>52</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" ht="50.1" customHeight="1">
       <c r="A63" s="1" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D63" s="1">
         <v>5616</v>
@@ -3936,20 +4025,20 @@
         <v>176</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" ht="50.1" customHeight="1">
       <c r="A64" s="1" t="s">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D64" s="1">
         <v>9153</v>
       </c>
-      <c r="E64" s="121"/>
+      <c r="E64" s="120"/>
       <c r="F64" s="1">
         <v>2289</v>
       </c>
@@ -3963,20 +4052,20 @@
         <v>120</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" ht="50.1" customHeight="1">
       <c r="A65" s="1" t="s">
-        <v>149</v>
+        <v>83</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D65" s="1">
         <v>5613</v>
       </c>
-      <c r="E65" s="117"/>
+      <c r="E65" s="116"/>
       <c r="F65" s="1">
         <v>2204</v>
       </c>
@@ -3990,15 +4079,15 @@
         <v>215</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" ht="50.1" customHeight="1">
       <c r="A66" s="1" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D66" s="1">
         <v>5619</v>
@@ -4017,20 +4106,20 @@
         <v>142</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" ht="50.1" customHeight="1">
       <c r="A67" s="1" t="s">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D67" s="1">
         <v>9106</v>
       </c>
-      <c r="E67" s="118"/>
+      <c r="E67" s="117"/>
       <c r="F67" s="1">
         <v>3375</v>
       </c>
@@ -4044,20 +4133,20 @@
         <v>193</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" ht="50.1" customHeight="1">
       <c r="A68" s="1" t="s">
-        <v>155</v>
+        <v>86</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D68" s="1">
         <v>9148</v>
       </c>
-      <c r="E68" s="122"/>
+      <c r="E68" s="121"/>
       <c r="F68" s="1">
         <v>7487</v>
       </c>
@@ -4071,20 +4160,20 @@
         <v>97</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" ht="50.1" customHeight="1">
       <c r="A69" s="1" t="s">
-        <v>156</v>
+        <v>87</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D69" s="1">
         <v>9121</v>
       </c>
-      <c r="E69" s="123"/>
+      <c r="E69" s="122"/>
       <c r="F69" s="1">
         <v>452</v>
       </c>
@@ -4098,20 +4187,20 @@
         <v>124</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" ht="50.1" customHeight="1">
       <c r="A70" s="1" t="s">
-        <v>151</v>
+        <v>88</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D70" s="1">
         <v>5611</v>
       </c>
-      <c r="E70" s="119"/>
+      <c r="E70" s="118"/>
       <c r="F70" s="1">
         <v>333</v>
       </c>
@@ -4125,15 +4214,15 @@
         <v>194</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" ht="50.1" customHeight="1">
       <c r="A71" s="1" t="s">
-        <v>167</v>
+        <v>89</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D71" s="1">
         <v>9107</v>
@@ -4152,15 +4241,15 @@
         <v>150</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" ht="50.1" customHeight="1">
       <c r="A72" s="1" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D72" s="1">
         <v>5620</v>
@@ -4179,312 +4268,312 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" ht="50.1" customHeight="1">
       <c r="A73" s="1" t="s">
-        <v>172</v>
+        <v>91</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D73" s="1">
-        <v>5550</v>
-      </c>
-      <c r="E73" s="141"/>
+        <v>5842</v>
+      </c>
+      <c r="E73" s="69"/>
       <c r="F73" s="1">
-        <v>5845</v>
+        <v>112</v>
       </c>
       <c r="G73" s="1">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="H73" s="1">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="I73" s="1">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="50.1" customHeight="1">
       <c r="A74" s="1" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D74" s="1">
-        <v>5842</v>
-      </c>
-      <c r="E74" s="69"/>
+        <v>5756</v>
+      </c>
+      <c r="E74" s="67"/>
       <c r="F74" s="1">
-        <v>112</v>
+        <v>383</v>
       </c>
       <c r="G74" s="1">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="H74" s="1">
-        <v>131</v>
+        <v>173</v>
       </c>
       <c r="I74" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="50.1" customHeight="1">
       <c r="A75" s="1" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D75" s="1">
-        <v>5756</v>
-      </c>
-      <c r="E75" s="67"/>
+        <v>5622</v>
+      </c>
+      <c r="E75" s="64"/>
       <c r="F75" s="1">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="G75" s="1">
-        <v>171</v>
+        <v>100</v>
       </c>
       <c r="H75" s="1">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="I75" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A76" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D76" s="1">
+        <v>5792</v>
+      </c>
+      <c r="E76" s="68"/>
+      <c r="F76" s="1">
+        <v>7716</v>
+      </c>
+      <c r="G76" s="1">
+        <v>5</v>
+      </c>
+      <c r="H76" s="1">
+        <v>147</v>
+      </c>
+      <c r="I76" s="1">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A77" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D77" s="1">
+        <v>5612</v>
+      </c>
+      <c r="E77" s="59"/>
+      <c r="F77" s="1">
+        <v>2243</v>
+      </c>
+      <c r="G77" s="1">
         <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D76" s="1">
-        <v>5622</v>
-      </c>
-      <c r="E76" s="64"/>
-      <c r="F76" s="1">
-        <v>369</v>
-      </c>
-      <c r="G76" s="1">
-        <v>100</v>
-      </c>
-      <c r="H76" s="1">
-        <v>166</v>
-      </c>
-      <c r="I76" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D77" s="1">
-        <v>5792</v>
-      </c>
-      <c r="E77" s="68"/>
-      <c r="F77" s="1">
-        <v>7716</v>
-      </c>
-      <c r="G77" s="1">
-        <v>5</v>
       </c>
       <c r="H77" s="1">
         <v>147</v>
       </c>
       <c r="I77" s="1">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="50.1" customHeight="1">
       <c r="A78" s="1" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D78" s="1">
-        <v>5612</v>
-      </c>
-      <c r="E78" s="59"/>
+        <v>9091</v>
+      </c>
+      <c r="E78" s="72"/>
       <c r="F78" s="1">
-        <v>2243</v>
+        <v>355</v>
       </c>
       <c r="G78" s="1">
         <v>0</v>
       </c>
       <c r="H78" s="1">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I78" s="1">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="50.1" customHeight="1">
       <c r="A79" s="1" t="s">
-        <v>166</v>
+        <v>97</v>
       </c>
       <c r="B79" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D79" s="1">
+        <v>9152</v>
+      </c>
+      <c r="E79" s="137"/>
+      <c r="F79" s="1">
+        <v>575</v>
+      </c>
+      <c r="G79" s="1">
+        <v>106</v>
+      </c>
+      <c r="H79" s="1">
+        <v>128</v>
+      </c>
+      <c r="I79" s="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A80" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D80" s="1">
+        <v>5609</v>
+      </c>
+      <c r="E80" s="58"/>
+      <c r="F80" s="1">
+        <v>633</v>
+      </c>
+      <c r="G80" s="1">
+        <v>0</v>
+      </c>
+      <c r="H80" s="1">
+        <v>113</v>
+      </c>
+      <c r="I80" s="1">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A81" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D81" s="1">
+        <v>5502</v>
+      </c>
+      <c r="E81" s="54"/>
+      <c r="F81" s="1">
+        <v>5555</v>
+      </c>
+      <c r="G81" s="1">
+        <v>91</v>
+      </c>
+      <c r="H81" s="1">
+        <v>126</v>
+      </c>
+      <c r="I81" s="1">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A82" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D82" s="1">
+        <v>5579</v>
+      </c>
+      <c r="E82" s="57"/>
+      <c r="F82" s="1">
+        <v>7490</v>
+      </c>
+      <c r="G82" s="1">
+        <v>116</v>
+      </c>
+      <c r="H82" s="1">
+        <v>152</v>
+      </c>
+      <c r="I82" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A83" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D83" s="1">
+        <v>7710</v>
+      </c>
+      <c r="E83" s="144"/>
+      <c r="F83" s="1">
+        <v>7740</v>
+      </c>
+      <c r="G83" s="1">
         <v>55</v>
       </c>
-      <c r="C79" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D79" s="1">
-        <v>9091</v>
-      </c>
-      <c r="E79" s="72"/>
-      <c r="F79" s="1">
-        <v>355</v>
-      </c>
-      <c r="G79" s="1">
-        <v>0</v>
-      </c>
-      <c r="H79" s="1">
-        <v>148</v>
-      </c>
-      <c r="I79" s="1">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D80" s="1">
-        <v>9152</v>
-      </c>
-      <c r="E80" s="138"/>
-      <c r="F80" s="1">
-        <v>575</v>
-      </c>
-      <c r="G80" s="1">
-        <v>106</v>
-      </c>
-      <c r="H80" s="1">
-        <v>128</v>
-      </c>
-      <c r="I80" s="1">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D81" s="1">
-        <v>5609</v>
-      </c>
-      <c r="E81" s="58"/>
-      <c r="F81" s="1">
-        <v>633</v>
-      </c>
-      <c r="G81" s="1">
-        <v>0</v>
-      </c>
-      <c r="H81" s="1">
-        <v>113</v>
-      </c>
-      <c r="I81" s="1">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D82" s="1">
-        <v>5502</v>
-      </c>
-      <c r="E82" s="54"/>
-      <c r="F82" s="1">
-        <v>5555</v>
-      </c>
-      <c r="G82" s="1">
-        <v>91</v>
-      </c>
-      <c r="H82" s="1">
-        <v>126</v>
-      </c>
-      <c r="I82" s="1">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D83" s="1">
-        <v>5579</v>
-      </c>
-      <c r="E83" s="57"/>
-      <c r="F83" s="1">
-        <v>7490</v>
-      </c>
-      <c r="G83" s="1">
-        <v>116</v>
-      </c>
       <c r="H83" s="1">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="I83" s="1">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="50.1" customHeight="1">
       <c r="A84" s="1" t="s">
-        <v>61</v>
+        <v>102</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D84" s="1">
         <v>5508</v>
@@ -4503,15 +4592,15 @@
         <v>84</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" ht="50.1" customHeight="1">
       <c r="A85" s="1" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D85" s="1">
         <v>5691</v>
@@ -4530,15 +4619,15 @@
         <v>101</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" ht="50.1" customHeight="1">
       <c r="A86" s="1" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D86" s="1">
         <v>5521</v>
@@ -4557,1722 +4646,2159 @@
         <v>96</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" ht="50.1" customHeight="1">
       <c r="A87" s="1" t="s">
-        <v>152</v>
+        <v>105</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D87" s="1">
-        <v>5751</v>
-      </c>
-      <c r="E87" s="120"/>
+        <v>5540</v>
+      </c>
+      <c r="E87" s="140"/>
       <c r="F87" s="1">
-        <v>562</v>
+        <v>356</v>
       </c>
       <c r="G87" s="1">
         <v>0</v>
       </c>
       <c r="H87" s="1">
+        <v>120</v>
+      </c>
+      <c r="I87" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A88" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D88" s="1">
+        <v>5751</v>
+      </c>
+      <c r="E88" s="119"/>
+      <c r="F88" s="1">
+        <v>562</v>
+      </c>
+      <c r="G88" s="1">
+        <v>0</v>
+      </c>
+      <c r="H88" s="1">
         <v>109</v>
       </c>
-      <c r="I87" s="1">
+      <c r="I88" s="1">
         <v>97</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D88" s="1">
+    <row r="89" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A89" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D89" s="1">
         <v>9129</v>
       </c>
-      <c r="E88" s="124"/>
-      <c r="F88" s="1">
+      <c r="E89" s="123"/>
+      <c r="F89" s="1">
         <v>7531</v>
       </c>
-      <c r="G88" s="1">
+      <c r="G89" s="1">
         <v>123</v>
       </c>
-      <c r="H88" s="1">
+      <c r="H89" s="1">
         <v>103</v>
       </c>
-      <c r="I88" s="1">
+      <c r="I89" s="1">
         <v>84</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D89" s="1">
+    <row r="90" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A90" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D90" s="1">
         <v>5755</v>
       </c>
-      <c r="E89" s="66"/>
-      <c r="F89" s="1">
+      <c r="E90" s="66"/>
+      <c r="F90" s="1">
         <v>342</v>
       </c>
-      <c r="G89" s="1">
+      <c r="G90" s="1">
         <v>0</v>
       </c>
-      <c r="H89" s="1">
+      <c r="H90" s="1">
         <v>101</v>
       </c>
-      <c r="I89" s="1">
+      <c r="I90" s="1">
         <v>71</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D90" s="1">
+    <row r="91" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A91" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D91" s="1">
         <v>9151</v>
       </c>
-      <c r="E90" s="125"/>
-      <c r="F90" s="1">
+      <c r="E91" s="124"/>
+      <c r="F91" s="1">
         <v>7763</v>
       </c>
-      <c r="G90" s="1">
+      <c r="G91" s="1">
         <v>90</v>
       </c>
-      <c r="H90" s="1">
+      <c r="H91" s="1">
         <v>90</v>
       </c>
-      <c r="I90" s="1">
+      <c r="I91" s="1">
         <v>57</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D91" s="1">
+    <row r="92" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A92" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D92" s="1">
         <v>5617</v>
       </c>
-      <c r="E91" s="61"/>
-      <c r="F91" s="1">
+      <c r="E92" s="61"/>
+      <c r="F92" s="1">
         <v>2308</v>
       </c>
-      <c r="G91" s="1">
+      <c r="G92" s="1">
         <v>91</v>
       </c>
-      <c r="H91" s="1">
+      <c r="H92" s="1">
         <v>85</v>
       </c>
-      <c r="I91" s="1">
+      <c r="I92" s="1">
         <v>24</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D92" s="1">
+    <row r="93" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A93" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D93" s="1">
         <v>5615</v>
       </c>
-      <c r="E92" s="60"/>
-      <c r="F92" s="1">
+      <c r="E93" s="60"/>
+      <c r="F93" s="1">
         <v>3425</v>
       </c>
-      <c r="G92" s="1">
+      <c r="G93" s="1">
         <v>0</v>
       </c>
-      <c r="H92" s="1">
+      <c r="H93" s="1">
         <v>97</v>
       </c>
-      <c r="I92" s="1">
+      <c r="I93" s="1">
         <v>64</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D93" s="1">
+    <row r="94" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A94" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D94" s="1">
         <v>5849</v>
       </c>
-      <c r="E93" s="70"/>
-      <c r="F93" s="1">
+      <c r="E94" s="70"/>
+      <c r="F94" s="1">
         <v>7722</v>
       </c>
-      <c r="G93" s="1">
+      <c r="G94" s="1">
         <v>2</v>
       </c>
-      <c r="H93" s="1">
+      <c r="H94" s="1">
         <v>78</v>
       </c>
-      <c r="I93" s="1">
+      <c r="I94" s="1">
         <v>79</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D94" s="1">
+    <row r="95" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A95" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D95" s="146">
+        <v>1001</v>
+      </c>
+      <c r="E95" s="147"/>
+      <c r="F95" s="1">
+        <v>1255</v>
+      </c>
+      <c r="G95" s="1">
+        <v>176</v>
+      </c>
+      <c r="H95" s="1">
+        <v>132</v>
+      </c>
+      <c r="I95" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A96" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D96" s="146">
+        <v>1002</v>
+      </c>
+      <c r="E96" s="148"/>
+      <c r="F96" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G96" s="1">
+        <v>218</v>
+      </c>
+      <c r="H96" s="1">
+        <v>217</v>
+      </c>
+      <c r="I96" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A97" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D97" s="1">
         <v>9008</v>
       </c>
-      <c r="E94" s="126"/>
-      <c r="F94" s="1">
+      <c r="E97" s="125"/>
+      <c r="F97" s="1">
         <v>164</v>
-      </c>
-      <c r="G94" s="1">
-        <v>255</v>
-      </c>
-      <c r="H94" s="1">
-        <v>124</v>
-      </c>
-      <c r="I94" s="1">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D95" s="1">
-        <v>5630</v>
-      </c>
-      <c r="E95" s="24"/>
-      <c r="F95" s="1">
-        <v>1575</v>
-      </c>
-      <c r="G95" s="1">
-        <v>255</v>
-      </c>
-      <c r="H95" s="1">
-        <v>123</v>
-      </c>
-      <c r="I95" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D96" s="1">
-        <v>9157</v>
-      </c>
-      <c r="E96" s="10"/>
-      <c r="F96" s="1">
-        <v>2010</v>
-      </c>
-      <c r="G96" s="1">
-        <v>255</v>
-      </c>
-      <c r="H96" s="1">
-        <v>174</v>
-      </c>
-      <c r="I96" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D97" s="1">
-        <v>5769</v>
-      </c>
-      <c r="E97" s="25"/>
-      <c r="F97" s="1">
-        <v>165</v>
       </c>
       <c r="G97" s="1">
         <v>255</v>
       </c>
       <c r="H97" s="1">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="I97" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="50.1" customHeight="1">
       <c r="A98" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>59</v>
+        <v>118</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>169</v>
+        <v>11</v>
       </c>
       <c r="D98" s="1">
-        <v>9072</v>
-      </c>
-      <c r="E98" s="22"/>
+        <v>5630</v>
+      </c>
+      <c r="E98" s="24"/>
       <c r="F98" s="1">
-        <v>1655</v>
+        <v>1575</v>
       </c>
       <c r="G98" s="1">
         <v>255</v>
       </c>
       <c r="H98" s="1">
+        <v>123</v>
+      </c>
+      <c r="I98" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A99" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D99" s="1">
+        <v>9157</v>
+      </c>
+      <c r="E99" s="10"/>
+      <c r="F99" s="1">
+        <v>2010</v>
+      </c>
+      <c r="G99" s="1">
+        <v>255</v>
+      </c>
+      <c r="H99" s="1">
+        <v>174</v>
+      </c>
+      <c r="I99" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A100" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D100" s="1">
+        <v>5518</v>
+      </c>
+      <c r="E100" s="141"/>
+      <c r="F100" s="1">
+        <v>1585</v>
+      </c>
+      <c r="G100" s="1">
+        <v>255</v>
+      </c>
+      <c r="H100" s="1">
+        <v>102</v>
+      </c>
+      <c r="I100" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A101" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D101" s="1">
+        <v>5769</v>
+      </c>
+      <c r="E101" s="25"/>
+      <c r="F101" s="1">
+        <v>165</v>
+      </c>
+      <c r="G101" s="1">
+        <v>255</v>
+      </c>
+      <c r="H101" s="1">
+        <v>97</v>
+      </c>
+      <c r="I101" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A102" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D102" s="1">
+        <v>5536</v>
+      </c>
+      <c r="E102" s="22"/>
+      <c r="F102" s="1">
+        <v>1655</v>
+      </c>
+      <c r="G102" s="1">
+        <v>255</v>
+      </c>
+      <c r="H102" s="1">
         <v>68</v>
       </c>
-      <c r="I98" s="1">
+      <c r="I102" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D99" s="1">
+    <row r="103" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A103" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D103" s="1">
+        <v>9072</v>
+      </c>
+      <c r="E103" s="22"/>
+      <c r="F103" s="1">
+        <v>1655</v>
+      </c>
+      <c r="G103" s="1">
+        <v>255</v>
+      </c>
+      <c r="H103" s="1">
+        <v>68</v>
+      </c>
+      <c r="I103" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A104" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D104" s="1">
         <v>5589</v>
       </c>
-      <c r="E99" s="23"/>
-      <c r="F99" s="1">
+      <c r="E104" s="23"/>
+      <c r="F104" s="1">
         <v>159</v>
       </c>
-      <c r="G99" s="1">
+      <c r="G104" s="1">
         <v>213</v>
       </c>
-      <c r="H99" s="1">
+      <c r="H104" s="1">
         <v>90</v>
       </c>
-      <c r="I99" s="1">
+      <c r="I104" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
+    <row r="105" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A105" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D105" s="1">
+        <v>7713</v>
+      </c>
+      <c r="E105" s="26"/>
+      <c r="F105" s="1">
+        <v>173</v>
+      </c>
+      <c r="G105" s="1">
+        <v>215</v>
+      </c>
+      <c r="H105" s="1">
+        <v>62</v>
+      </c>
+      <c r="I105" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A106" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D106" s="1">
+        <v>5543</v>
+      </c>
+      <c r="E106" s="91"/>
+      <c r="F106" s="1">
+        <v>684</v>
+      </c>
+      <c r="G106" s="1">
+        <v>231</v>
+      </c>
+      <c r="H106" s="1">
+        <v>197</v>
+      </c>
+      <c r="I106" s="1">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A107" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D107" s="1">
+        <v>5523</v>
+      </c>
+      <c r="E107" s="89"/>
+      <c r="F107" s="1">
+        <v>1895</v>
+      </c>
+      <c r="G107" s="1">
+        <v>249</v>
+      </c>
+      <c r="H107" s="1">
+        <v>181</v>
+      </c>
+      <c r="I107" s="1">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A108" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D108" s="1">
+        <v>5537</v>
+      </c>
+      <c r="E108" s="90"/>
+      <c r="F108" s="1">
+        <v>189</v>
+      </c>
+      <c r="G108" s="1">
+        <v>253</v>
+      </c>
+      <c r="H108" s="1">
+        <v>162</v>
+      </c>
+      <c r="I108" s="1">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A109" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D109" s="1">
+        <v>5599</v>
+      </c>
+      <c r="E109" s="92"/>
+      <c r="F109" s="1">
+        <v>501</v>
+      </c>
+      <c r="G109" s="1">
+        <v>222</v>
+      </c>
+      <c r="H109" s="1">
+        <v>165</v>
+      </c>
+      <c r="I109" s="1">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A110" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D110" s="1">
+        <v>9168</v>
+      </c>
+      <c r="E110" s="94"/>
+      <c r="F110" s="1">
+        <v>2038</v>
+      </c>
+      <c r="G110" s="1">
+        <v>247</v>
+      </c>
+      <c r="H110" s="1">
+        <v>90</v>
+      </c>
+      <c r="I110" s="1">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A111" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D111" s="1">
+        <v>7709</v>
+      </c>
+      <c r="E111" s="97"/>
+      <c r="F111" s="1">
+        <v>184</v>
+      </c>
+      <c r="G111" s="1">
+        <v>254</v>
+      </c>
+      <c r="H111" s="1">
+        <v>75</v>
+      </c>
+      <c r="I111" s="1">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A112" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D112" s="1">
+        <v>5591</v>
+      </c>
+      <c r="E112" s="96"/>
+      <c r="F112" s="1">
+        <v>215</v>
+      </c>
+      <c r="G112" s="1">
+        <v>180</v>
+      </c>
+      <c r="H112" s="1">
+        <v>11</v>
+      </c>
+      <c r="I112" s="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A113" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D113" s="1">
+        <v>5804</v>
+      </c>
+      <c r="E113" s="96"/>
+      <c r="F113" s="1">
+        <v>215</v>
+      </c>
+      <c r="G113" s="1">
+        <v>180</v>
+      </c>
+      <c r="H113" s="1">
+        <v>11</v>
+      </c>
+      <c r="I113" s="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A114" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D114" s="1">
+        <v>5586</v>
+      </c>
+      <c r="E114" s="52"/>
+      <c r="F114" s="1">
+        <v>2645</v>
+      </c>
+      <c r="G114" s="1">
+        <v>179</v>
+      </c>
+      <c r="H114" s="1">
+        <v>149</v>
+      </c>
+      <c r="I114" s="1">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A115" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D115" s="1">
+        <v>9098</v>
+      </c>
+      <c r="E115" s="126"/>
+      <c r="F115" s="1">
+        <v>2052</v>
+      </c>
+      <c r="G115" s="1">
+        <v>206</v>
+      </c>
+      <c r="H115" s="1">
+        <v>158</v>
+      </c>
+      <c r="I115" s="1">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A116" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D116" s="1">
+        <v>5592</v>
+      </c>
+      <c r="E116" s="53"/>
+      <c r="F116" s="1">
+        <v>680</v>
+      </c>
+      <c r="G116" s="1">
+        <v>200</v>
+      </c>
+      <c r="H116" s="1">
+        <v>148</v>
+      </c>
+      <c r="I116" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A117" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D117" s="1">
+        <v>9064</v>
+      </c>
+      <c r="E117" s="129"/>
+      <c r="F117" s="1">
+        <v>5285</v>
+      </c>
+      <c r="G117" s="1">
+        <v>141</v>
+      </c>
+      <c r="H117" s="1">
+        <v>136</v>
+      </c>
+      <c r="I117" s="1">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A118" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D118" s="1">
+        <v>9088</v>
+      </c>
+      <c r="E118" s="127"/>
+      <c r="F118" s="1">
+        <v>2074</v>
+      </c>
+      <c r="G118" s="1">
+        <v>153</v>
+      </c>
+      <c r="H118" s="1">
+        <v>104</v>
+      </c>
+      <c r="I118" s="1">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A119" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D119" s="1">
+        <v>9049</v>
+      </c>
+      <c r="E119" s="130"/>
+      <c r="F119" s="1">
+        <v>2725</v>
+      </c>
+      <c r="G119" s="1">
+        <v>105</v>
+      </c>
+      <c r="H119" s="1">
+        <v>91</v>
+      </c>
+      <c r="I119" s="1">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A120" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D120" s="1">
+        <v>9031</v>
+      </c>
+      <c r="E120" s="131"/>
+      <c r="F120" s="1">
+        <v>2102</v>
+      </c>
+      <c r="G120" s="1">
+        <v>106</v>
+      </c>
+      <c r="H120" s="1">
+        <v>86</v>
+      </c>
+      <c r="I120" s="1">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A121" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D121" s="1">
+        <v>5554</v>
+      </c>
+      <c r="E121" s="138"/>
+      <c r="F121" s="1">
+        <v>7662</v>
+      </c>
+      <c r="G121" s="1">
+        <v>127</v>
+      </c>
+      <c r="H121" s="1">
+        <v>62</v>
+      </c>
+      <c r="I121" s="1">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A122" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D122" s="1">
+        <v>9021</v>
+      </c>
+      <c r="E122" s="132"/>
+      <c r="F122" s="1">
+        <v>267</v>
+      </c>
+      <c r="G122" s="1">
+        <v>101</v>
+      </c>
+      <c r="H122" s="1">
+        <v>33</v>
+      </c>
+      <c r="I122" s="1">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A123" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D123" s="1">
+        <v>9027</v>
+      </c>
+      <c r="E123" s="95"/>
+      <c r="F123" s="1">
+        <v>683</v>
+      </c>
+      <c r="G123" s="1">
+        <v>130</v>
+      </c>
+      <c r="H123" s="1">
+        <v>34</v>
+      </c>
+      <c r="I123" s="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A124" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D124" s="1">
+        <v>9055</v>
+      </c>
+      <c r="E124" s="43"/>
+      <c r="F124" s="1">
+        <v>209</v>
+      </c>
+      <c r="G124" s="1">
+        <v>116</v>
+      </c>
+      <c r="H124" s="1">
+        <v>33</v>
+      </c>
+      <c r="I124" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A125" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D125" s="1">
+        <v>9053</v>
+      </c>
+      <c r="E125" s="128"/>
+      <c r="F125" s="1">
+        <v>2627</v>
+      </c>
+      <c r="G125" s="1">
+        <v>63</v>
+      </c>
+      <c r="H125" s="1">
+        <v>14</v>
+      </c>
+      <c r="I125" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A126" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D126" s="1">
+        <v>9023</v>
+      </c>
+      <c r="E126" s="133"/>
+      <c r="F126" s="1">
+        <v>2345</v>
+      </c>
+      <c r="G126" s="1">
+        <v>255</v>
+      </c>
+      <c r="H126" s="1">
+        <v>104</v>
+      </c>
+      <c r="I126" s="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A127" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D127" s="1">
+        <v>5566</v>
+      </c>
+      <c r="E127" s="47"/>
+      <c r="F127" s="1">
+        <v>199</v>
+      </c>
+      <c r="G127" s="1">
+        <v>226</v>
+      </c>
+      <c r="H127" s="1">
+        <v>3</v>
+      </c>
+      <c r="I127" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A128" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D128" s="1">
+        <v>5563</v>
+      </c>
+      <c r="E128" s="46"/>
+      <c r="F128" s="1">
+        <v>186</v>
+      </c>
+      <c r="G128" s="1">
+        <v>212</v>
+      </c>
+      <c r="H128" s="1">
+        <v>1</v>
+      </c>
+      <c r="I128" s="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A129" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D129" s="1">
+        <v>5678</v>
+      </c>
+      <c r="E129" s="48"/>
+      <c r="F129" s="1">
+        <v>193</v>
+      </c>
+      <c r="G129" s="1">
+        <v>201</v>
+      </c>
+      <c r="H129" s="1">
+        <v>1</v>
+      </c>
+      <c r="I129" s="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A130" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D130" s="1">
+        <v>9002</v>
+      </c>
+      <c r="E130" s="134"/>
+      <c r="F130" s="1">
+        <v>7621</v>
+      </c>
+      <c r="G130" s="1">
+        <v>182</v>
+      </c>
+      <c r="H130" s="1">
+        <v>20</v>
+      </c>
+      <c r="I130" s="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A131" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D131" s="1">
+        <v>5807</v>
+      </c>
+      <c r="E131" s="51"/>
+      <c r="F131" s="1">
+        <v>207</v>
+      </c>
+      <c r="G131" s="1">
+        <v>176</v>
+      </c>
+      <c r="H131" s="1">
+        <v>0</v>
+      </c>
+      <c r="I131" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A132" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D132" s="1">
+        <v>5549</v>
+      </c>
+      <c r="E132" s="44"/>
+      <c r="F132" s="1">
+        <v>7420</v>
+      </c>
+      <c r="G132" s="1">
+        <v>163</v>
+      </c>
+      <c r="H132" s="1">
+        <v>22</v>
+      </c>
+      <c r="I132" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A133" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D133" s="1">
+        <v>5552</v>
+      </c>
+      <c r="E133" s="45"/>
+      <c r="F133" s="1">
+        <v>208</v>
+      </c>
+      <c r="G133" s="1">
+        <v>142</v>
+      </c>
+      <c r="H133" s="1">
+        <v>20</v>
+      </c>
+      <c r="I133" s="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A134" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D134" s="1">
+        <v>5634</v>
+      </c>
+      <c r="E134" s="49"/>
+      <c r="F134" s="1">
+        <v>7622</v>
+      </c>
+      <c r="G134" s="1">
+        <v>154</v>
+      </c>
+      <c r="H134" s="1">
         <v>29</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D100" s="1">
-        <v>7713</v>
-      </c>
-      <c r="E100" s="26"/>
-      <c r="F100" s="1">
-        <v>173</v>
-      </c>
-      <c r="G100" s="1">
-        <v>215</v>
-      </c>
-      <c r="H100" s="1">
-        <v>62</v>
-      </c>
-      <c r="I100" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D101" s="1">
-        <v>5543</v>
-      </c>
-      <c r="E101" s="91"/>
-      <c r="F101" s="1">
-        <v>684</v>
-      </c>
-      <c r="G101" s="1">
-        <v>231</v>
-      </c>
-      <c r="H101" s="1">
-        <v>197</v>
-      </c>
-      <c r="I101" s="1">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D102" s="1">
-        <v>5523</v>
-      </c>
-      <c r="E102" s="89"/>
-      <c r="F102" s="1">
-        <v>1895</v>
-      </c>
-      <c r="G102" s="1">
-        <v>249</v>
-      </c>
-      <c r="H102" s="1">
-        <v>181</v>
-      </c>
-      <c r="I102" s="1">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D103" s="1">
-        <v>5537</v>
-      </c>
-      <c r="E103" s="90"/>
-      <c r="F103" s="1">
-        <v>189</v>
-      </c>
-      <c r="G103" s="1">
-        <v>253</v>
-      </c>
-      <c r="H103" s="1">
+      <c r="I134" s="1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A135" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D135" s="1">
+        <v>5796</v>
+      </c>
+      <c r="E135" s="50"/>
+      <c r="F135" s="1">
+        <v>7421</v>
+      </c>
+      <c r="G135" s="1">
+        <v>108</v>
+      </c>
+      <c r="H135" s="1">
+        <v>23</v>
+      </c>
+      <c r="I135" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A136" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D136" s="1">
+        <v>5597</v>
+      </c>
+      <c r="E136" s="99"/>
+      <c r="F136" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="I103" s="1">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D104" s="1">
-        <v>5599</v>
-      </c>
-      <c r="E104" s="92"/>
-      <c r="F104" s="1">
-        <v>501</v>
-      </c>
-      <c r="G104" s="1">
-        <v>222</v>
-      </c>
-      <c r="H104" s="1">
+      <c r="G136" s="1">
+        <v>255</v>
+      </c>
+      <c r="H136" s="1">
+        <v>255</v>
+      </c>
+      <c r="I136" s="1">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A137" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D137" s="1">
+        <v>5643</v>
+      </c>
+      <c r="E137" s="7"/>
+      <c r="F137" s="1">
+        <v>7499</v>
+      </c>
+      <c r="G137" s="1">
+        <v>244</v>
+      </c>
+      <c r="H137" s="1">
+        <v>228</v>
+      </c>
+      <c r="I137" s="1">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A138" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="I104" s="1">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D105" s="1">
-        <v>9168</v>
-      </c>
-      <c r="E105" s="94"/>
-      <c r="F105" s="1">
-        <v>2038</v>
-      </c>
-      <c r="G105" s="1">
-        <v>247</v>
-      </c>
-      <c r="H105" s="1">
-        <v>90</v>
-      </c>
-      <c r="I105" s="1">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D106" s="1">
-        <v>7709</v>
-      </c>
-      <c r="E106" s="97"/>
-      <c r="F106" s="1">
-        <v>184</v>
-      </c>
-      <c r="G106" s="1">
-        <v>254</v>
-      </c>
-      <c r="H106" s="1">
-        <v>75</v>
-      </c>
-      <c r="I106" s="1">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D107" s="1">
-        <v>5591</v>
-      </c>
-      <c r="E107" s="96"/>
-      <c r="F107" s="1">
-        <v>215</v>
-      </c>
-      <c r="G107" s="1">
-        <v>180</v>
-      </c>
-      <c r="H107" s="1">
-        <v>11</v>
-      </c>
-      <c r="I107" s="1">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D108" s="1">
-        <v>5804</v>
-      </c>
-      <c r="E108" s="96"/>
-      <c r="F108" s="1">
-        <v>215</v>
-      </c>
-      <c r="G108" s="1">
-        <v>180</v>
-      </c>
-      <c r="H108" s="1">
-        <v>11</v>
-      </c>
-      <c r="I108" s="1">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D109" s="1">
-        <v>5586</v>
-      </c>
-      <c r="E109" s="52"/>
-      <c r="F109" s="1">
-        <v>2645</v>
-      </c>
-      <c r="G109" s="1">
-        <v>179</v>
-      </c>
-      <c r="H109" s="1">
-        <v>149</v>
-      </c>
-      <c r="I109" s="1">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D110" s="1">
-        <v>9098</v>
-      </c>
-      <c r="E110" s="127"/>
-      <c r="F110" s="1">
-        <v>2052</v>
-      </c>
-      <c r="G110" s="1">
-        <v>206</v>
-      </c>
-      <c r="H110" s="1">
-        <v>158</v>
-      </c>
-      <c r="I110" s="1">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D111" s="1">
-        <v>5592</v>
-      </c>
-      <c r="E111" s="53"/>
-      <c r="F111" s="1">
-        <v>680</v>
-      </c>
-      <c r="G111" s="1">
-        <v>200</v>
-      </c>
-      <c r="H111" s="1">
-        <v>148</v>
-      </c>
-      <c r="I111" s="1">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D112" s="1">
-        <v>9064</v>
-      </c>
-      <c r="E112" s="130"/>
-      <c r="F112" s="1">
-        <v>5285</v>
-      </c>
-      <c r="G112" s="1">
-        <v>141</v>
-      </c>
-      <c r="H112" s="1">
-        <v>136</v>
-      </c>
-      <c r="I112" s="1">
+      <c r="B138" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="113" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D113" s="1">
-        <v>9088</v>
-      </c>
-      <c r="E113" s="128"/>
-      <c r="F113" s="1">
-        <v>2074</v>
-      </c>
-      <c r="G113" s="1">
-        <v>153</v>
-      </c>
-      <c r="H113" s="1">
-        <v>104</v>
-      </c>
-      <c r="I113" s="1">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D114" s="1">
-        <v>9049</v>
-      </c>
-      <c r="E114" s="131"/>
-      <c r="F114" s="1">
-        <v>2725</v>
-      </c>
-      <c r="G114" s="1">
-        <v>105</v>
-      </c>
-      <c r="H114" s="1">
-        <v>91</v>
-      </c>
-      <c r="I114" s="1">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D115" s="1">
-        <v>9031</v>
-      </c>
-      <c r="E115" s="132"/>
-      <c r="F115" s="1">
-        <v>2102</v>
-      </c>
-      <c r="G115" s="1">
-        <v>106</v>
-      </c>
-      <c r="H115" s="1">
-        <v>86</v>
-      </c>
-      <c r="I115" s="1">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D116" s="1">
-        <v>5554</v>
-      </c>
-      <c r="E116" s="139"/>
-      <c r="F116" s="1">
-        <v>7662</v>
-      </c>
-      <c r="G116" s="1">
-        <v>127</v>
-      </c>
-      <c r="H116" s="1">
-        <v>62</v>
-      </c>
-      <c r="I116" s="1">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D117" s="1">
-        <v>9021</v>
-      </c>
-      <c r="E117" s="133"/>
-      <c r="F117" s="1">
-        <v>267</v>
-      </c>
-      <c r="G117" s="1">
-        <v>101</v>
-      </c>
-      <c r="H117" s="1">
-        <v>33</v>
-      </c>
-      <c r="I117" s="1">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D118" s="1">
-        <v>9027</v>
-      </c>
-      <c r="E118" s="95"/>
-      <c r="F118" s="1">
-        <v>683</v>
-      </c>
-      <c r="G118" s="1">
-        <v>130</v>
-      </c>
-      <c r="H118" s="1">
-        <v>34</v>
-      </c>
-      <c r="I118" s="1">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D119" s="1">
-        <v>9055</v>
-      </c>
-      <c r="E119" s="43"/>
-      <c r="F119" s="1">
-        <v>209</v>
-      </c>
-      <c r="G119" s="1">
-        <v>116</v>
-      </c>
-      <c r="H119" s="1">
-        <v>33</v>
-      </c>
-      <c r="I119" s="1">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D120" s="1">
-        <v>9053</v>
-      </c>
-      <c r="E120" s="129"/>
-      <c r="F120" s="1">
-        <v>2627</v>
-      </c>
-      <c r="G120" s="1">
-        <v>63</v>
-      </c>
-      <c r="H120" s="1">
-        <v>14</v>
-      </c>
-      <c r="I120" s="1">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D121" s="1">
-        <v>9023</v>
-      </c>
-      <c r="E121" s="134"/>
-      <c r="F121" s="1">
-        <v>2345</v>
-      </c>
-      <c r="G121" s="1">
-        <v>255</v>
-      </c>
-      <c r="H121" s="1">
-        <v>104</v>
-      </c>
-      <c r="I121" s="1">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D122" s="1">
-        <v>5566</v>
-      </c>
-      <c r="E122" s="47"/>
-      <c r="F122" s="1">
-        <v>199</v>
-      </c>
-      <c r="G122" s="1">
-        <v>226</v>
-      </c>
-      <c r="H122" s="1">
-        <v>3</v>
-      </c>
-      <c r="I122" s="1">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D123" s="1">
-        <v>5563</v>
-      </c>
-      <c r="E123" s="46"/>
-      <c r="F123" s="1">
-        <v>186</v>
-      </c>
-      <c r="G123" s="1">
-        <v>212</v>
-      </c>
-      <c r="H123" s="1">
-        <v>1</v>
-      </c>
-      <c r="I123" s="1">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D124" s="1">
-        <v>5678</v>
-      </c>
-      <c r="E124" s="48"/>
-      <c r="F124" s="1">
-        <v>193</v>
-      </c>
-      <c r="G124" s="1">
-        <v>201</v>
-      </c>
-      <c r="H124" s="1">
-        <v>1</v>
-      </c>
-      <c r="I124" s="1">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D125" s="1">
-        <v>9002</v>
-      </c>
-      <c r="E125" s="135"/>
-      <c r="F125" s="1">
-        <v>7621</v>
-      </c>
-      <c r="G125" s="1">
-        <v>182</v>
-      </c>
-      <c r="H125" s="1">
-        <v>20</v>
-      </c>
-      <c r="I125" s="1">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D126" s="1">
-        <v>5807</v>
-      </c>
-      <c r="E126" s="51"/>
-      <c r="F126" s="1">
-        <v>207</v>
-      </c>
-      <c r="G126" s="1">
-        <v>176</v>
-      </c>
-      <c r="H126" s="1">
-        <v>0</v>
-      </c>
-      <c r="I126" s="1">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D127" s="1">
-        <v>5549</v>
-      </c>
-      <c r="E127" s="44"/>
-      <c r="F127" s="1">
-        <v>7420</v>
-      </c>
-      <c r="G127" s="1">
-        <v>163</v>
-      </c>
-      <c r="H127" s="1">
-        <v>22</v>
-      </c>
-      <c r="I127" s="1">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D128" s="1">
-        <v>5552</v>
-      </c>
-      <c r="E128" s="45"/>
-      <c r="F128" s="1">
-        <v>208</v>
-      </c>
-      <c r="G128" s="1">
-        <v>142</v>
-      </c>
-      <c r="H128" s="1">
-        <v>20</v>
-      </c>
-      <c r="I128" s="1">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D129" s="1">
-        <v>5634</v>
-      </c>
-      <c r="E129" s="49"/>
-      <c r="F129" s="1">
-        <v>7622</v>
-      </c>
-      <c r="G129" s="1">
-        <v>154</v>
-      </c>
-      <c r="H129" s="1">
-        <v>29</v>
-      </c>
-      <c r="I129" s="1">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D130" s="1">
-        <v>5796</v>
-      </c>
-      <c r="E130" s="50"/>
-      <c r="F130" s="1">
-        <v>7421</v>
-      </c>
-      <c r="G130" s="1">
-        <v>108</v>
-      </c>
-      <c r="H130" s="1">
-        <v>23</v>
-      </c>
-      <c r="I130" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D131" s="1">
-        <v>5597</v>
-      </c>
-      <c r="E131" s="99"/>
-      <c r="F131" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G131" s="1">
-        <v>255</v>
-      </c>
-      <c r="H131" s="1">
-        <v>255</v>
-      </c>
-      <c r="I131" s="1">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D132" s="1">
-        <v>5643</v>
-      </c>
-      <c r="E132" s="7"/>
-      <c r="F132" s="1">
-        <v>7499</v>
-      </c>
-      <c r="G132" s="1">
-        <v>244</v>
-      </c>
-      <c r="H132" s="1">
-        <v>228</v>
-      </c>
-      <c r="I132" s="1">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D133" s="1">
+      <c r="C138" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D138" s="1">
         <v>9028</v>
       </c>
-      <c r="E133" s="5"/>
-      <c r="F133" s="1">
+      <c r="E138" s="5"/>
+      <c r="F138" s="1">
         <v>7401</v>
       </c>
-      <c r="G133" s="1">
+      <c r="G138" s="1">
         <v>248</v>
-      </c>
-      <c r="H133" s="1">
-        <v>224</v>
-      </c>
-      <c r="I133" s="1">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D134" s="1">
-        <v>9034</v>
-      </c>
-      <c r="E134" s="93"/>
-      <c r="F134" s="1">
-        <v>475</v>
-      </c>
-      <c r="G134" s="1">
-        <v>245</v>
-      </c>
-      <c r="H134" s="1">
-        <v>207</v>
-      </c>
-      <c r="I134" s="1">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D135" s="1">
-        <v>5698</v>
-      </c>
-      <c r="E135" s="8"/>
-      <c r="F135" s="1">
-        <v>1355</v>
-      </c>
-      <c r="G135" s="1">
-        <v>254</v>
-      </c>
-      <c r="H135" s="1">
-        <v>197</v>
-      </c>
-      <c r="I135" s="1">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D136" s="1">
-        <v>5625</v>
-      </c>
-      <c r="E136" s="6"/>
-      <c r="F136" s="1">
-        <v>100</v>
-      </c>
-      <c r="G136" s="1">
-        <v>249</v>
-      </c>
-      <c r="H136" s="1">
-        <v>235</v>
-      </c>
-      <c r="I136" s="1">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D137" s="1">
-        <v>5713</v>
-      </c>
-      <c r="E137" s="142"/>
-      <c r="F137" s="1">
-        <v>388</v>
-      </c>
-      <c r="G137" s="1">
-        <v>233</v>
-      </c>
-      <c r="H137" s="1">
-        <v>240</v>
-      </c>
-      <c r="I137" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D138" s="1">
-        <v>5762</v>
-      </c>
-      <c r="E138" s="9"/>
-      <c r="F138" s="1">
-        <v>107</v>
-      </c>
-      <c r="G138" s="1">
-        <v>254</v>
       </c>
       <c r="H138" s="1">
         <v>224</v>
       </c>
       <c r="I138" s="1">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A139" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D139" s="1">
+        <v>9034</v>
+      </c>
+      <c r="E139" s="93"/>
+      <c r="F139" s="1">
+        <v>475</v>
+      </c>
+      <c r="G139" s="1">
+        <v>245</v>
+      </c>
+      <c r="H139" s="1">
+        <v>207</v>
+      </c>
+      <c r="I139" s="1">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A140" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D140" s="1">
+        <v>5698</v>
+      </c>
+      <c r="E140" s="8"/>
+      <c r="F140" s="1">
+        <v>1355</v>
+      </c>
+      <c r="G140" s="1">
+        <v>254</v>
+      </c>
+      <c r="H140" s="1">
+        <v>197</v>
+      </c>
+      <c r="I140" s="1">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A141" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D141" s="1">
+        <v>5625</v>
+      </c>
+      <c r="E141" s="6"/>
+      <c r="F141" s="1">
+        <v>100</v>
+      </c>
+      <c r="G141" s="1">
+        <v>249</v>
+      </c>
+      <c r="H141" s="1">
+        <v>235</v>
+      </c>
+      <c r="I141" s="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A142" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D142" s="1">
+        <v>5713</v>
+      </c>
+      <c r="E142" s="139"/>
+      <c r="F142" s="1">
+        <v>388</v>
+      </c>
+      <c r="G142" s="1">
+        <v>233</v>
+      </c>
+      <c r="H142" s="1">
+        <v>240</v>
+      </c>
+      <c r="I142" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A143" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D143" s="1">
+        <v>5762</v>
+      </c>
+      <c r="E143" s="9"/>
+      <c r="F143" s="1">
+        <v>107</v>
+      </c>
+      <c r="G143" s="1">
+        <v>254</v>
+      </c>
+      <c r="H143" s="1">
+        <v>224</v>
+      </c>
+      <c r="I143" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C139" s="1" t="s">
+    <row r="144" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A144" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D144" s="1">
+        <v>5542</v>
+      </c>
+      <c r="E144" s="4"/>
+      <c r="F144" s="1">
+        <v>116</v>
+      </c>
+      <c r="G144" s="1">
+        <v>253</v>
+      </c>
+      <c r="H144" s="1">
+        <v>206</v>
+      </c>
+      <c r="I144" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A145" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D145" s="1">
+        <v>9172</v>
+      </c>
+      <c r="E145" s="4"/>
+      <c r="F145" s="1">
+        <v>116</v>
+      </c>
+      <c r="G145" s="1">
+        <v>253</v>
+      </c>
+      <c r="H145" s="1">
+        <v>206</v>
+      </c>
+      <c r="I145" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A146" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D146" s="1">
+        <v>5765</v>
+      </c>
+      <c r="E146" s="11"/>
+      <c r="F146" s="1">
+        <v>136</v>
+      </c>
+      <c r="G146" s="1">
+        <v>255</v>
+      </c>
+      <c r="H146" s="1">
+        <v>191</v>
+      </c>
+      <c r="I146" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A147" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D147" s="1">
+        <v>9109</v>
+      </c>
+      <c r="E147" s="11"/>
+      <c r="F147" s="1">
+        <v>136</v>
+      </c>
+      <c r="G147" s="1">
+        <v>255</v>
+      </c>
+      <c r="H147" s="1">
+        <v>191</v>
+      </c>
+      <c r="I147" s="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A148" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D148" s="1">
+        <v>9001</v>
+      </c>
+      <c r="E148" s="135"/>
+      <c r="F148" s="1">
+        <v>7406</v>
+      </c>
+      <c r="G148" s="1">
+        <v>245</v>
+      </c>
+      <c r="H148" s="1">
+        <v>196</v>
+      </c>
+      <c r="I148" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A149" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D149" s="1">
+        <v>5513</v>
+      </c>
+      <c r="E149" s="2"/>
+      <c r="F149" s="1">
+        <v>137</v>
+      </c>
+      <c r="G149" s="1">
+        <v>255</v>
+      </c>
+      <c r="H149" s="1">
+        <v>163</v>
+      </c>
+      <c r="I149" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A150" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D150" s="1">
+        <v>5709</v>
+      </c>
+      <c r="E150" s="2"/>
+      <c r="F150" s="1">
+        <v>137</v>
+      </c>
+      <c r="G150" s="1">
+        <v>255</v>
+      </c>
+      <c r="H150" s="1">
+        <v>163</v>
+      </c>
+      <c r="I150" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A151" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D151" s="1">
+        <v>9125</v>
+      </c>
+      <c r="E151" s="88"/>
+      <c r="F151" s="1">
+        <v>466</v>
+      </c>
+      <c r="G151" s="1">
+        <v>203</v>
+      </c>
+      <c r="H151" s="1">
         <v>169</v>
       </c>
-      <c r="D139" s="1">
-        <v>5542</v>
-      </c>
-      <c r="E139" s="4"/>
-      <c r="F139" s="1">
-        <v>116</v>
-      </c>
-      <c r="G139" s="1">
-        <v>253</v>
-      </c>
-      <c r="H139" s="1">
-        <v>206</v>
-      </c>
-      <c r="I139" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D140" s="1">
-        <v>9127</v>
-      </c>
-      <c r="E140" s="143"/>
-      <c r="F140" s="1">
-        <v>7548</v>
-      </c>
-      <c r="G140" s="1">
-        <v>255</v>
-      </c>
-      <c r="H140" s="1">
-        <v>199</v>
-      </c>
-      <c r="I140" s="1">
+      <c r="I151" s="1">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A152" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D152" s="1">
+        <v>9005</v>
+      </c>
+      <c r="E152" s="136"/>
+      <c r="F152" s="1">
+        <v>7752</v>
+      </c>
+      <c r="G152" s="1">
+        <v>210</v>
+      </c>
+      <c r="H152" s="1">
+        <v>175</v>
+      </c>
+      <c r="I152" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A153" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D153" s="1">
+        <v>5906</v>
+      </c>
+      <c r="E153" s="13"/>
+      <c r="F153" s="1">
+        <v>7407</v>
+      </c>
+      <c r="G153" s="1">
+        <v>207</v>
+      </c>
+      <c r="H153" s="1">
+        <v>160</v>
+      </c>
+      <c r="I153" s="1">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" ht="50.1" customHeight="1">
+      <c r="A154" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D154" s="1">
+        <v>5771</v>
+      </c>
+      <c r="E154" s="12"/>
+      <c r="F154" s="1">
+        <v>117</v>
+      </c>
+      <c r="G154" s="1">
+        <v>205</v>
+      </c>
+      <c r="H154" s="1">
+        <v>151</v>
+      </c>
+      <c r="I154" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D141" s="1">
-        <v>5765</v>
-      </c>
-      <c r="E141" s="11"/>
-      <c r="F141" s="1">
-        <v>136</v>
-      </c>
-      <c r="G141" s="1">
-        <v>255</v>
-      </c>
-      <c r="H141" s="1">
-        <v>191</v>
-      </c>
-      <c r="I141" s="1">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="142" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D142" s="1">
-        <v>9109</v>
-      </c>
-      <c r="E142" s="11"/>
-      <c r="F142" s="1">
-        <v>136</v>
-      </c>
-      <c r="G142" s="1">
-        <v>255</v>
-      </c>
-      <c r="H142" s="1">
-        <v>191</v>
-      </c>
-      <c r="I142" s="1">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="143" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D143" s="1">
-        <v>9001</v>
-      </c>
-      <c r="E143" s="136"/>
-      <c r="F143" s="1">
-        <v>7406</v>
-      </c>
-      <c r="G143" s="1">
-        <v>245</v>
-      </c>
-      <c r="H143" s="1">
-        <v>196</v>
-      </c>
-      <c r="I143" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D144" s="1">
-        <v>5513</v>
-      </c>
-      <c r="E144" s="2"/>
-      <c r="F144" s="1">
-        <v>137</v>
-      </c>
-      <c r="G144" s="1">
-        <v>255</v>
-      </c>
-      <c r="H144" s="1">
-        <v>163</v>
-      </c>
-      <c r="I144" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D145" s="1">
-        <v>5709</v>
-      </c>
-      <c r="E145" s="2"/>
-      <c r="F145" s="1">
-        <v>137</v>
-      </c>
-      <c r="G145" s="1">
-        <v>255</v>
-      </c>
-      <c r="H145" s="1">
-        <v>163</v>
-      </c>
-      <c r="I145" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="146" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D146" s="1">
-        <v>9125</v>
-      </c>
-      <c r="E146" s="88"/>
-      <c r="F146" s="1">
-        <v>466</v>
-      </c>
-      <c r="G146" s="1">
-        <v>203</v>
-      </c>
-      <c r="H146" s="1">
-        <v>169</v>
-      </c>
-      <c r="I146" s="1">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="147" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D147" s="1">
-        <v>9005</v>
-      </c>
-      <c r="E147" s="137"/>
-      <c r="F147" s="1">
-        <v>7752</v>
-      </c>
-      <c r="G147" s="1">
-        <v>210</v>
-      </c>
-      <c r="H147" s="1">
-        <v>175</v>
-      </c>
-      <c r="I147" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="148" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D148" s="1">
-        <v>5906</v>
-      </c>
-      <c r="E148" s="13"/>
-      <c r="F148" s="1">
-        <v>7407</v>
-      </c>
-      <c r="G148" s="1">
-        <v>207</v>
-      </c>
-      <c r="H148" s="1">
-        <v>160</v>
-      </c>
-      <c r="I148" s="1">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D149" s="1">
-        <v>5771</v>
-      </c>
-      <c r="E149" s="12"/>
-      <c r="F149" s="1">
-        <v>117</v>
-      </c>
-      <c r="G149" s="1">
-        <v>205</v>
-      </c>
-      <c r="H149" s="1">
-        <v>151</v>
-      </c>
-      <c r="I149" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" spans="1:9" ht="50.1" hidden="1" customHeight="1"/>
+    <row r="156" spans="1:9" ht="50.1" hidden="1" customHeight="1"/>
+    <row r="157" spans="1:9" ht="50.1" hidden="1" customHeight="1"/>
+    <row r="158" spans="1:9" ht="50.1" hidden="1" customHeight="1"/>
+    <row r="159" spans="1:9" ht="50.1" hidden="1" customHeight="1"/>
+    <row r="160" spans="1:9" ht="50.1" hidden="1" customHeight="1"/>
+    <row r="161" ht="50.1" hidden="1" customHeight="1"/>
+    <row r="162" ht="50.1" hidden="1" customHeight="1"/>
+    <row r="163" ht="50.1" hidden="1" customHeight="1"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="c3ClYhs0N2OhBtrHFU58YJMaHZCmOEhH07Fkko7okwJGCtWPvtkC6a/l1y9dvAl/x8ygg3/ENCd6vAdMBaKpLg==" saltValue="gdVgeTjoh3FnBM1XaW2N/g==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection sort="0" autoFilter="0"/>
   <protectedRanges>
-    <protectedRange sqref="A1:I149" name="AllowSortFilter"/>
+    <protectedRange sqref="A1:I154" name="AllowSortFilter"/>
   </protectedRanges>
-  <autoFilter ref="A1:I149" xr:uid="{0F5A48E9-F316-4B13-8BCA-A06BACA98426}"/>
+  <autoFilter ref="A1:I154" xr:uid="{0F5A48E9-F316-4B13-8BCA-A06BACA98426}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DEDC398-C089-4BC9-AE96-3C477BFA0288}">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" customWidth="1"/>
+    <col min="4" max="4" width="24.42578125" customWidth="1"/>
+    <col min="5" max="5" width="31" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" customWidth="1"/>
+    <col min="7" max="9" width="9.140625" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" hidden="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="3" customFormat="1" ht="50.1" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1670</v>
+      </c>
+      <c r="E2" s="145"/>
+      <c r="F2" s="1">
+        <v>7508</v>
+      </c>
+      <c r="G2" s="1">
+        <v>227</v>
+      </c>
+      <c r="H2" s="1">
+        <v>184</v>
+      </c>
+      <c r="I2" s="1">
+        <v>123</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sort="0" autoFilter="0"/>
+  <protectedRanges>
+    <protectedRange sqref="A1:I2" name="AllowSortFilter"/>
+  </protectedRanges>
+  <autoFilter ref="A1:I1" xr:uid="{6DEDC398-C089-4BC9-AE96-3C477BFA0288}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A1C7DD37AE641E4B9B3FD2F75B2D99BC" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6b9cb41f595aff4764e09aef2b23c1ed">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ea7a09a4-fe73-437e-8a86-996460e9b058" xmlns:ns3="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="daad8a4a6daff5298e6b89d91afce8e3" ns2:_="" ns3:_="">
+    <xsd:import namespace="ea7a09a4-fe73-437e-8a86-996460e9b058"/>
+    <xsd:import namespace="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ea7a09a4-fe73-437e-8a86-996460e9b058" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="d2f5926c-fefe-46c4-85d9-9ef0eea46f5c" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{6fbb2a74-2168-4404-a595-59f9a11d4eed}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea7a09a4-fe73-437e-8a86-996460e9b058">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C65B8C05-791C-44F7-9E6F-9BD7A4092E1F}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F449F58-D4CB-4A41-A107-1F236EAEFFCE}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8FEEB8D-1293-4CED-BC80-EB3354C12A79}"/>
 </file>